--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -46276,13 +46276,13 @@
         <v>2</v>
       </c>
       <c r="AW210" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX210" t="n">
         <v>4</v>
       </c>
       <c r="AY210" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AZ210" t="n">
         <v>6</v>
@@ -46712,13 +46712,13 @@
         <v>3</v>
       </c>
       <c r="AW212" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AX212" t="n">
         <v>8</v>
       </c>
       <c r="AY212" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AZ212" t="n">
         <v>11</v>

--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP213"/>
+  <dimension ref="A1:BP216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -914,7 +914,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="AP4" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ4" t="n">
         <v>0.5</v>
@@ -1786,7 +1786,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ6" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR6" t="n">
         <v>0</v>
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.62</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ13" t="n">
         <v>1</v>
@@ -4620,7 +4620,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR19" t="n">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ22" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR22" t="n">
         <v>1.87</v>
@@ -6797,7 +6797,7 @@
         <v>3</v>
       </c>
       <c r="AP29" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ29" t="n">
         <v>0.62</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.33</v>
@@ -7454,7 +7454,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ32" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR32" t="n">
         <v>1.42</v>
@@ -8105,7 +8105,7 @@
         <v>0</v>
       </c>
       <c r="AP35" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ35" t="n">
         <v>0.92</v>
@@ -8544,7 +8544,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ37" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR37" t="n">
         <v>1.5</v>
@@ -9198,7 +9198,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ40" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR40" t="n">
         <v>1.33</v>
@@ -11160,7 +11160,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ49" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR49" t="n">
         <v>1.57</v>
@@ -11378,7 +11378,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ50" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR50" t="n">
         <v>1.48</v>
@@ -11811,7 +11811,7 @@
         <v>3</v>
       </c>
       <c r="AP52" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ52" t="n">
         <v>2.67</v>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ53" t="n">
         <v>0.33</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.83</v>
@@ -12468,7 +12468,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR55" t="n">
         <v>1.71</v>
@@ -14863,10 +14863,10 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ66" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR66" t="n">
         <v>1.59</v>
@@ -15299,7 +15299,7 @@
         <v>1</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ68" t="n">
         <v>0.62</v>
@@ -15520,7 +15520,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ69" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR69" t="n">
         <v>1.46</v>
@@ -16174,7 +16174,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ72" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR72" t="n">
         <v>1.62</v>
@@ -16389,7 +16389,7 @@
         <v>1.33</v>
       </c>
       <c r="AP73" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ73" t="n">
         <v>0.83</v>
@@ -17482,7 +17482,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR78" t="n">
         <v>1.47</v>
@@ -18572,7 +18572,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ83" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR83" t="n">
         <v>1.5</v>
@@ -19226,7 +19226,7 @@
         <v>2</v>
       </c>
       <c r="AQ86" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR86" t="n">
         <v>1.68</v>
@@ -19441,7 +19441,7 @@
         <v>2</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.92</v>
@@ -20095,7 +20095,7 @@
         <v>1</v>
       </c>
       <c r="AP90" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ90" t="n">
         <v>0.91</v>
@@ -20313,7 +20313,7 @@
         <v>1</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ91" t="n">
         <v>0.83</v>
@@ -21624,7 +21624,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ97" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR97" t="n">
         <v>2.37</v>
@@ -22496,7 +22496,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ101" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR101" t="n">
         <v>1.27</v>
@@ -23801,7 +23801,7 @@
         <v>1.17</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.42</v>
@@ -24019,10 +24019,10 @@
         <v>1.2</v>
       </c>
       <c r="AP108" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR108" t="n">
         <v>1.56</v>
@@ -24676,7 +24676,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ111" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR111" t="n">
         <v>1.31</v>
@@ -25109,7 +25109,7 @@
         <v>2.6</v>
       </c>
       <c r="AP113" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ113" t="n">
         <v>2.67</v>
@@ -25981,7 +25981,7 @@
         <v>0.83</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.5</v>
@@ -26420,7 +26420,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ119" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR119" t="n">
         <v>1.33</v>
@@ -26856,7 +26856,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ121" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR121" t="n">
         <v>1.18</v>
@@ -27289,7 +27289,7 @@
         <v>0.67</v>
       </c>
       <c r="AP123" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
         <v>0.91</v>
@@ -28818,7 +28818,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ130" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR130" t="n">
         <v>1.57</v>
@@ -29033,7 +29033,7 @@
         <v>2</v>
       </c>
       <c r="AP131" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ131" t="n">
         <v>1.83</v>
@@ -29469,7 +29469,7 @@
         <v>1.57</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.17</v>
@@ -30341,7 +30341,7 @@
         <v>1.88</v>
       </c>
       <c r="AP137" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ137" t="n">
         <v>1.92</v>
@@ -31652,7 +31652,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR143" t="n">
         <v>2.41</v>
@@ -31867,7 +31867,7 @@
         <v>1.5</v>
       </c>
       <c r="AP144" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ144" t="n">
         <v>1.17</v>
@@ -32742,7 +32742,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ148" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR148" t="n">
         <v>1.93</v>
@@ -34701,7 +34701,7 @@
         <v>1.25</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -35137,7 +35137,7 @@
         <v>1.25</v>
       </c>
       <c r="AP159" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ159" t="n">
         <v>0.92</v>
@@ -35358,7 +35358,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ160" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR160" t="n">
         <v>1.4</v>
@@ -35791,7 +35791,7 @@
         <v>1.88</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ162" t="n">
         <v>1.83</v>
@@ -36012,7 +36012,7 @@
         <v>0.83</v>
       </c>
       <c r="AQ163" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR163" t="n">
         <v>1.3</v>
@@ -36666,7 +36666,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ166" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR166" t="n">
         <v>1.42</v>
@@ -37538,7 +37538,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ170" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR170" t="n">
         <v>1.41</v>
@@ -37974,7 +37974,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ172" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR172" t="n">
         <v>1.61</v>
@@ -38625,7 +38625,7 @@
         <v>1.63</v>
       </c>
       <c r="AP175" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ175" t="n">
         <v>1.55</v>
@@ -39279,7 +39279,7 @@
         <v>2.78</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ178" t="n">
         <v>2.67</v>
@@ -39497,10 +39497,10 @@
         <v>0.9</v>
       </c>
       <c r="AP179" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ179" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR179" t="n">
         <v>1.68</v>
@@ -41462,7 +41462,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ188" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AR188" t="n">
         <v>1.6</v>
@@ -42113,7 +42113,7 @@
         <v>1.1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.92</v>
@@ -42331,7 +42331,7 @@
         <v>1.2</v>
       </c>
       <c r="AP192" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AQ192" t="n">
         <v>1</v>
@@ -42770,7 +42770,7 @@
         <v>2</v>
       </c>
       <c r="AQ194" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AR194" t="n">
         <v>1.66</v>
@@ -43203,7 +43203,7 @@
         <v>0.9</v>
       </c>
       <c r="AP196" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AQ196" t="n">
         <v>0.75</v>
@@ -43642,7 +43642,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ198" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR198" t="n">
         <v>1.91</v>
@@ -46988,6 +46988,660 @@
       </c>
       <c r="BP213" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>213</v>
+      </c>
+      <c r="B214" t="n">
+        <v>8227600</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E214" s="2" t="n">
+        <v>46082.47916666666</v>
+      </c>
+      <c r="F214" t="n">
+        <v>24</v>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I214" t="n">
+        <v>3</v>
+      </c>
+      <c r="J214" t="n">
+        <v>0</v>
+      </c>
+      <c r="K214" t="n">
+        <v>3</v>
+      </c>
+      <c r="L214" t="n">
+        <v>4</v>
+      </c>
+      <c r="M214" t="n">
+        <v>0</v>
+      </c>
+      <c r="N214" t="n">
+        <v>4</v>
+      </c>
+      <c r="O214" t="inlineStr">
+        <is>
+          <t>['21', '30', '42', '90+5']</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q214" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="R214" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S214" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="T214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U214" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V214" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="W214" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="X214" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="Y214" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z214" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AA214" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="AB214" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AC214" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD214" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE214" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF214" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG214" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AH214" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AI214" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AJ214" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AK214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL214" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM214" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AN214" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP214" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AQ214" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR214" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AS214" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AT214" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AU214" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV214" t="n">
+        <v>3</v>
+      </c>
+      <c r="AW214" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX214" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY214" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ214" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA214" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB214" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC214" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD214" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BE214" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="BF214" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="BG214" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="BH214" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BI214" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="BJ214" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BK214" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BL214" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BM214" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BN214" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO214" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BP214" t="n">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>214</v>
+      </c>
+      <c r="B215" t="n">
+        <v>8227708</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E215" s="2" t="n">
+        <v>46082.5625</v>
+      </c>
+      <c r="F215" t="n">
+        <v>24</v>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I215" t="n">
+        <v>0</v>
+      </c>
+      <c r="J215" t="n">
+        <v>0</v>
+      </c>
+      <c r="K215" t="n">
+        <v>0</v>
+      </c>
+      <c r="L215" t="n">
+        <v>2</v>
+      </c>
+      <c r="M215" t="n">
+        <v>0</v>
+      </c>
+      <c r="N215" t="n">
+        <v>2</v>
+      </c>
+      <c r="O215" t="inlineStr">
+        <is>
+          <t>['64', '81']</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="Q215" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R215" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="S215" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U215" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="V215" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W215" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="X215" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y215" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z215" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AA215" t="n">
+        <v>3.81</v>
+      </c>
+      <c r="AB215" t="n">
+        <v>3.31</v>
+      </c>
+      <c r="AC215" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD215" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE215" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF215" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AG215" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI215" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ215" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AK215" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL215" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM215" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN215" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AP215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AQ215" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AR215" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AS215" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AT215" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU215" t="n">
+        <v>7</v>
+      </c>
+      <c r="AV215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AW215" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX215" t="n">
+        <v>2</v>
+      </c>
+      <c r="AY215" t="n">
+        <v>15</v>
+      </c>
+      <c r="AZ215" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA215" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB215" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC215" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD215" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BE215" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF215" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG215" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BH215" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="BI215" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BJ215" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BK215" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BL215" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BM215" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="BN215" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BO215" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BP215" t="n">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>215</v>
+      </c>
+      <c r="B216" t="n">
+        <v>8227690</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E216" s="2" t="n">
+        <v>46082.64583333334</v>
+      </c>
+      <c r="F216" t="n">
+        <v>24</v>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I216" t="n">
+        <v>1</v>
+      </c>
+      <c r="J216" t="n">
+        <v>1</v>
+      </c>
+      <c r="K216" t="n">
+        <v>2</v>
+      </c>
+      <c r="L216" t="n">
+        <v>1</v>
+      </c>
+      <c r="M216" t="n">
+        <v>2</v>
+      </c>
+      <c r="N216" t="n">
+        <v>3</v>
+      </c>
+      <c r="O216" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>['36', '50']</t>
+        </is>
+      </c>
+      <c r="Q216" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S216" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T216" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U216" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="W216" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="X216" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y216" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z216" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="AA216" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AB216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AC216" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD216" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE216" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AF216" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AG216" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH216" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI216" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ216" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AK216" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL216" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM216" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN216" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AP216" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AQ216" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AR216" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AS216" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AT216" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AU216" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV216" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW216" t="n">
+        <v>4</v>
+      </c>
+      <c r="AX216" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY216" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ216" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA216" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB216" t="n">
+        <v>9</v>
+      </c>
+      <c r="BC216" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD216" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BE216" t="n">
+        <v>6.65</v>
+      </c>
+      <c r="BF216" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BG216" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BH216" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="BI216" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BJ216" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BK216" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="BL216" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM216" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN216" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BO216" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="BP216" t="n">
+        <v>1.38</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP216"/>
+  <dimension ref="A1:BP217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2873,7 +2873,7 @@
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ11" t="n">
         <v>0.62</v>
@@ -3530,7 +3530,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -7015,7 +7015,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ30" t="n">
         <v>0.33</v>
@@ -9416,7 +9416,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR41" t="n">
         <v>1.62</v>
@@ -12247,7 +12247,7 @@
         <v>2</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ54" t="n">
         <v>0.83</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR59" t="n">
         <v>1.47</v>
@@ -14863,7 +14863,7 @@
         <v>1</v>
       </c>
       <c r="AP66" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ66" t="n">
         <v>0.92</v>
@@ -17918,7 +17918,7 @@
         <v>2.58</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR80" t="n">
         <v>2.46</v>
@@ -19441,7 +19441,7 @@
         <v>2</v>
       </c>
       <c r="AP87" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ87" t="n">
         <v>1.92</v>
@@ -21406,7 +21406,7 @@
         <v>0.75</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR96" t="n">
         <v>1.58</v>
@@ -23801,7 +23801,7 @@
         <v>1.17</v>
       </c>
       <c r="AP107" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ107" t="n">
         <v>1.42</v>
@@ -24894,7 +24894,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR112" t="n">
         <v>1.39</v>
@@ -25981,7 +25981,7 @@
         <v>0.83</v>
       </c>
       <c r="AP117" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ117" t="n">
         <v>0.5</v>
@@ -29469,7 +29469,7 @@
         <v>1.57</v>
       </c>
       <c r="AP133" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ133" t="n">
         <v>1.17</v>
@@ -29690,7 +29690,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR134" t="n">
         <v>1.9</v>
@@ -34268,7 +34268,7 @@
         <v>2</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR155" t="n">
         <v>1.7</v>
@@ -34701,7 +34701,7 @@
         <v>1.25</v>
       </c>
       <c r="AP157" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
         <v>1</v>
@@ -38628,7 +38628,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR175" t="n">
         <v>1.46</v>
@@ -39279,7 +39279,7 @@
         <v>2.78</v>
       </c>
       <c r="AP178" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ178" t="n">
         <v>2.67</v>
@@ -41244,7 +41244,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR187" t="n">
         <v>1.25</v>
@@ -42113,7 +42113,7 @@
         <v>1.1</v>
       </c>
       <c r="AP191" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ191" t="n">
         <v>0.92</v>
@@ -44296,7 +44296,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AR201" t="n">
         <v>1.35</v>
@@ -47563,7 +47563,7 @@
         <v>1.64</v>
       </c>
       <c r="AP216" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="AQ216" t="n">
         <v>1.75</v>
@@ -47642,6 +47642,224 @@
       </c>
       <c r="BP216" t="n">
         <v>1.38</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>216</v>
+      </c>
+      <c r="B217" t="n">
+        <v>8227756</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E217" s="2" t="n">
+        <v>46085.6875</v>
+      </c>
+      <c r="F217" t="n">
+        <v>17</v>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I217" t="n">
+        <v>0</v>
+      </c>
+      <c r="J217" t="n">
+        <v>0</v>
+      </c>
+      <c r="K217" t="n">
+        <v>0</v>
+      </c>
+      <c r="L217" t="n">
+        <v>0</v>
+      </c>
+      <c r="M217" t="n">
+        <v>1</v>
+      </c>
+      <c r="N217" t="n">
+        <v>1</v>
+      </c>
+      <c r="O217" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>['73']</t>
+        </is>
+      </c>
+      <c r="Q217" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R217" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="S217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T217" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="U217" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V217" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="W217" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="X217" t="n">
+        <v>5.95</v>
+      </c>
+      <c r="Y217" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z217" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA217" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AB217" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC217" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD217" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE217" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG217" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AH217" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI217" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ217" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL217" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM217" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN217" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AP217" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ217" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AR217" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS217" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AT217" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="AU217" t="n">
+        <v>3</v>
+      </c>
+      <c r="AV217" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW217" t="n">
+        <v>7</v>
+      </c>
+      <c r="AX217" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY217" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ217" t="n">
+        <v>14</v>
+      </c>
+      <c r="BA217" t="n">
+        <v>2</v>
+      </c>
+      <c r="BB217" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC217" t="n">
+        <v>9</v>
+      </c>
+      <c r="BD217" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BE217" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BF217" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="BG217" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="BH217" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI217" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="BJ217" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BK217" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="BL217" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="BM217" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="BN217" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="BO217" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="BP217" t="n">
+        <v>1.34</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP217"/>
+  <dimension ref="A1:BP223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ2" t="n">
         <v>1.75</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ5" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR5" t="n">
         <v>0</v>
@@ -1783,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ6" t="n">
         <v>0.92</v>
@@ -2004,7 +2004,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ7" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR7" t="n">
         <v>0</v>
@@ -2658,7 +2658,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR10" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR13" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR14" t="n">
         <v>0</v>
@@ -3745,7 +3745,7 @@
         <v>0</v>
       </c>
       <c r="AP15" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ15" t="n">
         <v>0.33</v>
@@ -4181,7 +4181,7 @@
         <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ17" t="n">
         <v>0.83</v>
@@ -5053,7 +5053,7 @@
         <v>3</v>
       </c>
       <c r="AP21" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ21" t="n">
         <v>0.75</v>
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ23" t="n">
         <v>1.92</v>
@@ -5707,10 +5707,10 @@
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ24" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR24" t="n">
         <v>1.66</v>
@@ -5928,7 +5928,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR25" t="n">
         <v>0.85</v>
@@ -6143,10 +6143,10 @@
         <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ26" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR26" t="n">
         <v>2.26</v>
@@ -6364,7 +6364,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ27" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR27" t="n">
         <v>1.61</v>
@@ -7887,7 +7887,7 @@
         <v>2</v>
       </c>
       <c r="AP34" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ34" t="n">
         <v>0.75</v>
@@ -8326,7 +8326,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ36" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR36" t="n">
         <v>1.43</v>
@@ -8759,7 +8759,7 @@
         <v>1.5</v>
       </c>
       <c r="AP38" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ38" t="n">
         <v>0.5</v>
@@ -8977,10 +8977,10 @@
         <v>1.5</v>
       </c>
       <c r="AP39" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ39" t="n">
         <v>0.83</v>
-      </c>
-      <c r="AQ39" t="n">
-        <v>0.91</v>
       </c>
       <c r="AR39" t="n">
         <v>0.7</v>
@@ -9195,7 +9195,7 @@
         <v>1.5</v>
       </c>
       <c r="AP40" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ40" t="n">
         <v>1.75</v>
@@ -9416,7 +9416,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ41" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR41" t="n">
         <v>1.62</v>
@@ -10067,10 +10067,10 @@
         <v>3</v>
       </c>
       <c r="AP44" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ44" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR44" t="n">
         <v>1.74</v>
@@ -10288,7 +10288,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ45" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR45" t="n">
         <v>1.71</v>
@@ -10506,7 +10506,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ46" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR46" t="n">
         <v>1.49</v>
@@ -12686,7 +12686,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ56" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR56" t="n">
         <v>1.39</v>
@@ -12901,7 +12901,7 @@
         <v>1</v>
       </c>
       <c r="AP57" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ57" t="n">
         <v>0.5</v>
@@ -13122,7 +13122,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ58" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR58" t="n">
         <v>1.7</v>
@@ -13340,7 +13340,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ59" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR59" t="n">
         <v>1.47</v>
@@ -13555,10 +13555,10 @@
         <v>1</v>
       </c>
       <c r="AP60" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ60" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR60" t="n">
         <v>1.52</v>
@@ -13773,10 +13773,10 @@
         <v>0.67</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ61" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR61" t="n">
         <v>2.01</v>
@@ -13991,7 +13991,7 @@
         <v>2.33</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ62" t="n">
         <v>1.92</v>
@@ -14209,7 +14209,7 @@
         <v>2</v>
       </c>
       <c r="AP63" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ63" t="n">
         <v>1.17</v>
@@ -14430,7 +14430,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR64" t="n">
         <v>1.64</v>
@@ -17043,10 +17043,10 @@
         <v>1.5</v>
       </c>
       <c r="AP76" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ76" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR76" t="n">
         <v>1.67</v>
@@ -17261,7 +17261,7 @@
         <v>1.75</v>
       </c>
       <c r="AP77" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ77" t="n">
         <v>1.17</v>
@@ -17700,7 +17700,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ79" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR79" t="n">
         <v>1.51</v>
@@ -17915,10 +17915,10 @@
         <v>2.33</v>
       </c>
       <c r="AP80" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ80" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR80" t="n">
         <v>2.46</v>
@@ -18136,7 +18136,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR81" t="n">
         <v>1.54</v>
@@ -18351,10 +18351,10 @@
         <v>2.5</v>
       </c>
       <c r="AP82" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ82" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR82" t="n">
         <v>1.61</v>
@@ -19877,7 +19877,7 @@
         <v>0.75</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ89" t="n">
         <v>0.62</v>
@@ -20098,7 +20098,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ90" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR90" t="n">
         <v>1.86</v>
@@ -20534,7 +20534,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR92" t="n">
         <v>1.43</v>
@@ -20752,7 +20752,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR93" t="n">
         <v>1.35</v>
@@ -20970,7 +20970,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR94" t="n">
         <v>1.9</v>
@@ -21185,10 +21185,10 @@
         <v>1</v>
       </c>
       <c r="AP95" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ95" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR95" t="n">
         <v>1.43</v>
@@ -21403,10 +21403,10 @@
         <v>1.75</v>
       </c>
       <c r="AP96" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ96" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR96" t="n">
         <v>1.58</v>
@@ -21621,7 +21621,7 @@
         <v>1</v>
       </c>
       <c r="AP97" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ97" t="n">
         <v>0.6899999999999999</v>
@@ -22057,7 +22057,7 @@
         <v>1</v>
       </c>
       <c r="AP99" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ99" t="n">
         <v>0.5</v>
@@ -22714,7 +22714,7 @@
         <v>2</v>
       </c>
       <c r="AQ102" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR102" t="n">
         <v>1.61</v>
@@ -22929,7 +22929,7 @@
         <v>0.6</v>
       </c>
       <c r="AP103" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ103" t="n">
         <v>0.62</v>
@@ -23804,7 +23804,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR107" t="n">
         <v>1.7</v>
@@ -24237,7 +24237,7 @@
         <v>0.8</v>
       </c>
       <c r="AP109" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ109" t="n">
         <v>0.83</v>
@@ -24458,7 +24458,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ110" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR110" t="n">
         <v>1.47</v>
@@ -24673,7 +24673,7 @@
         <v>0.83</v>
       </c>
       <c r="AP111" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ111" t="n">
         <v>0.6899999999999999</v>
@@ -24894,7 +24894,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ112" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR112" t="n">
         <v>1.39</v>
@@ -25327,7 +25327,7 @@
         <v>1.2</v>
       </c>
       <c r="AP114" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ114" t="n">
         <v>0.92</v>
@@ -25763,7 +25763,7 @@
         <v>1.83</v>
       </c>
       <c r="AP116" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ116" t="n">
         <v>1.17</v>
@@ -26202,7 +26202,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ118" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR118" t="n">
         <v>1.86</v>
@@ -27074,7 +27074,7 @@
         <v>2</v>
       </c>
       <c r="AQ122" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR122" t="n">
         <v>1.63</v>
@@ -27292,7 +27292,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ123" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR123" t="n">
         <v>1.58</v>
@@ -27725,7 +27725,7 @@
         <v>2</v>
       </c>
       <c r="AP125" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ125" t="n">
         <v>1.92</v>
@@ -27943,7 +27943,7 @@
         <v>0.67</v>
       </c>
       <c r="AP126" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ126" t="n">
         <v>0.83</v>
@@ -28164,7 +28164,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ127" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR127" t="n">
         <v>1.68</v>
@@ -28382,7 +28382,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ128" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR128" t="n">
         <v>1.73</v>
@@ -28815,7 +28815,7 @@
         <v>0.71</v>
       </c>
       <c r="AP130" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ130" t="n">
         <v>0.6899999999999999</v>
@@ -29036,7 +29036,7 @@
         <v>2.42</v>
       </c>
       <c r="AQ131" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR131" t="n">
         <v>1.72</v>
@@ -29687,10 +29687,10 @@
         <v>1.67</v>
       </c>
       <c r="AP134" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ134" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR134" t="n">
         <v>1.9</v>
@@ -30123,7 +30123,7 @@
         <v>2.67</v>
       </c>
       <c r="AP136" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ136" t="n">
         <v>2.67</v>
@@ -30559,10 +30559,10 @@
         <v>0.29</v>
       </c>
       <c r="AP138" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ138" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR138" t="n">
         <v>1.63</v>
@@ -30777,7 +30777,7 @@
         <v>1</v>
       </c>
       <c r="AP139" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ139" t="n">
         <v>0.75</v>
@@ -31216,7 +31216,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ141" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR141" t="n">
         <v>1.83</v>
@@ -31434,7 +31434,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ142" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR142" t="n">
         <v>1.24</v>
@@ -31649,7 +31649,7 @@
         <v>1.43</v>
       </c>
       <c r="AP143" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ143" t="n">
         <v>0.92</v>
@@ -32521,7 +32521,7 @@
         <v>0.63</v>
       </c>
       <c r="AP147" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ147" t="n">
         <v>0.62</v>
@@ -32739,7 +32739,7 @@
         <v>1</v>
       </c>
       <c r="AP148" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ148" t="n">
         <v>0.6899999999999999</v>
@@ -33178,7 +33178,7 @@
         <v>2</v>
       </c>
       <c r="AQ150" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR150" t="n">
         <v>1.61</v>
@@ -33829,7 +33829,7 @@
         <v>0.38</v>
       </c>
       <c r="AP153" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ153" t="n">
         <v>0.33</v>
@@ -34268,7 +34268,7 @@
         <v>2</v>
       </c>
       <c r="AQ155" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR155" t="n">
         <v>1.7</v>
@@ -34704,7 +34704,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ157" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR157" t="n">
         <v>1.49</v>
@@ -34919,7 +34919,7 @@
         <v>2.75</v>
       </c>
       <c r="AP158" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ158" t="n">
         <v>2.67</v>
@@ -35576,7 +35576,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ161" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR161" t="n">
         <v>1.48</v>
@@ -35794,7 +35794,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR162" t="n">
         <v>1.52</v>
@@ -36009,7 +36009,7 @@
         <v>1.38</v>
       </c>
       <c r="AP163" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ163" t="n">
         <v>1.75</v>
@@ -36445,10 +36445,10 @@
         <v>0.5</v>
       </c>
       <c r="AP165" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ165" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR165" t="n">
         <v>2.38</v>
@@ -37102,7 +37102,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ168" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR168" t="n">
         <v>1.26</v>
@@ -37317,7 +37317,7 @@
         <v>1</v>
       </c>
       <c r="AP169" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ169" t="n">
         <v>0.75</v>
@@ -37756,7 +37756,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ171" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR171" t="n">
         <v>1.6</v>
@@ -38192,7 +38192,7 @@
         <v>1.33</v>
       </c>
       <c r="AQ173" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR173" t="n">
         <v>1.68</v>
@@ -38407,7 +38407,7 @@
         <v>0.67</v>
       </c>
       <c r="AP174" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ174" t="n">
         <v>0.83</v>
@@ -38628,7 +38628,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ175" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR175" t="n">
         <v>1.46</v>
@@ -40154,7 +40154,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ182" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR182" t="n">
         <v>1.35</v>
@@ -40369,7 +40369,7 @@
         <v>1.9</v>
       </c>
       <c r="AP183" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ183" t="n">
         <v>1.92</v>
@@ -40587,10 +40587,10 @@
         <v>0.33</v>
       </c>
       <c r="AP184" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ184" t="n">
         <v>0.83</v>
-      </c>
-      <c r="AQ184" t="n">
-        <v>0.64</v>
       </c>
       <c r="AR184" t="n">
         <v>1.27</v>
@@ -40808,7 +40808,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ185" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR185" t="n">
         <v>1.52</v>
@@ -41023,7 +41023,7 @@
         <v>0.6</v>
       </c>
       <c r="AP186" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ186" t="n">
         <v>0.5</v>
@@ -41244,7 +41244,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ187" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR187" t="n">
         <v>1.25</v>
@@ -41677,10 +41677,10 @@
         <v>2.1</v>
       </c>
       <c r="AP189" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ189" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR189" t="n">
         <v>2.33</v>
@@ -42334,7 +42334,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ192" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR192" t="n">
         <v>1.45</v>
@@ -43639,7 +43639,7 @@
         <v>1</v>
       </c>
       <c r="AP198" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ198" t="n">
         <v>0.92</v>
@@ -43860,7 +43860,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ199" t="n">
-        <v>0.64</v>
+        <v>0.83</v>
       </c>
       <c r="AR199" t="n">
         <v>1.5</v>
@@ -44078,7 +44078,7 @@
         <v>1.25</v>
       </c>
       <c r="AQ200" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AR200" t="n">
         <v>1.56</v>
@@ -44296,7 +44296,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ201" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR201" t="n">
         <v>1.35</v>
@@ -44511,10 +44511,10 @@
         <v>0.7</v>
       </c>
       <c r="AP202" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AQ202" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AR202" t="n">
         <v>1.58</v>
@@ -44729,7 +44729,7 @@
         <v>1.27</v>
       </c>
       <c r="AP203" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AQ203" t="n">
         <v>1.17</v>
@@ -44947,7 +44947,7 @@
         <v>2</v>
       </c>
       <c r="AP204" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AQ204" t="n">
         <v>1.92</v>
@@ -45165,10 +45165,10 @@
         <v>1.09</v>
       </c>
       <c r="AP205" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ205" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AR205" t="n">
         <v>1.59</v>
@@ -45601,10 +45601,10 @@
         <v>1.45</v>
       </c>
       <c r="AP207" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="AQ207" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AR207" t="n">
         <v>1.31</v>
@@ -47784,7 +47784,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ217" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AR217" t="n">
         <v>1.53</v>
@@ -47859,6 +47859,1314 @@
         <v>2.97</v>
       </c>
       <c r="BP217" t="n">
+        <v>1.34</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>217</v>
+      </c>
+      <c r="B218" t="n">
+        <v>8227599</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E218" s="2" t="n">
+        <v>46087.6875</v>
+      </c>
+      <c r="F218" t="n">
+        <v>25</v>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Bayern München</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Borussia M'gladbach</t>
+        </is>
+      </c>
+      <c r="I218" t="n">
+        <v>2</v>
+      </c>
+      <c r="J218" t="n">
+        <v>0</v>
+      </c>
+      <c r="K218" t="n">
+        <v>2</v>
+      </c>
+      <c r="L218" t="n">
+        <v>4</v>
+      </c>
+      <c r="M218" t="n">
+        <v>1</v>
+      </c>
+      <c r="N218" t="n">
+        <v>5</v>
+      </c>
+      <c r="O218" t="inlineStr">
+        <is>
+          <t>['33', '45+1', '57', '79']</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>['89']</t>
+        </is>
+      </c>
+      <c r="Q218" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="R218" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="S218" t="n">
+        <v>8</v>
+      </c>
+      <c r="T218" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="U218" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="V218" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="W218" t="n">
+        <v>2</v>
+      </c>
+      <c r="X218" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Y218" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z218" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AA218" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB218" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AC218" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD218" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE218" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF218" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AG218" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH218" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AI218" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AJ218" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AK218" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AL218" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM218" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AN218" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP218" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AQ218" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AR218" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AS218" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AT218" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AU218" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW218" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX218" t="n">
+        <v>5</v>
+      </c>
+      <c r="AY218" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ218" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB218" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC218" t="n">
+        <v>8</v>
+      </c>
+      <c r="BD218" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BE218" t="n">
+        <v>17</v>
+      </c>
+      <c r="BF218" t="n">
+        <v>7</v>
+      </c>
+      <c r="BG218" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH218" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI218" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BJ218" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK218" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BL218" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM218" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN218" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO218" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP218" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>218</v>
+      </c>
+      <c r="B219" t="n">
+        <v>8227715</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E219" s="2" t="n">
+        <v>46088.47916666666</v>
+      </c>
+      <c r="F219" t="n">
+        <v>25</v>
+      </c>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I219" t="n">
+        <v>0</v>
+      </c>
+      <c r="J219" t="n">
+        <v>1</v>
+      </c>
+      <c r="K219" t="n">
+        <v>1</v>
+      </c>
+      <c r="L219" t="n">
+        <v>2</v>
+      </c>
+      <c r="M219" t="n">
+        <v>1</v>
+      </c>
+      <c r="N219" t="n">
+        <v>3</v>
+      </c>
+      <c r="O219" t="inlineStr">
+        <is>
+          <t>['76', '90+2']</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>['39']</t>
+        </is>
+      </c>
+      <c r="Q219" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="R219" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="S219" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="T219" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="U219" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="V219" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="W219" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="X219" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="Y219" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z219" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AA219" t="n">
+        <v>5.15</v>
+      </c>
+      <c r="AB219" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AC219" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD219" t="n">
+        <v>21</v>
+      </c>
+      <c r="AE219" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AF219" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG219" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH219" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI219" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ219" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AK219" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AL219" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM219" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AN219" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP219" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ219" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR219" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AS219" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AT219" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="AU219" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV219" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW219" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX219" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY219" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ219" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA219" t="n">
+        <v>6</v>
+      </c>
+      <c r="BB219" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC219" t="n">
+        <v>14</v>
+      </c>
+      <c r="BD219" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BE219" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="BF219" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BG219" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="BH219" t="n">
+        <v>4</v>
+      </c>
+      <c r="BI219" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BJ219" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="BK219" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BL219" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BM219" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BN219" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="BO219" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BP219" t="n">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>219</v>
+      </c>
+      <c r="B220" t="n">
+        <v>8227598</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E220" s="2" t="n">
+        <v>46088.47916666666</v>
+      </c>
+      <c r="F220" t="n">
+        <v>25</v>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I220" t="n">
+        <v>0</v>
+      </c>
+      <c r="J220" t="n">
+        <v>2</v>
+      </c>
+      <c r="K220" t="n">
+        <v>2</v>
+      </c>
+      <c r="L220" t="n">
+        <v>2</v>
+      </c>
+      <c r="M220" t="n">
+        <v>4</v>
+      </c>
+      <c r="N220" t="n">
+        <v>6</v>
+      </c>
+      <c r="O220" t="inlineStr">
+        <is>
+          <t>['62', '84']</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>['26', '45+1', '49', '78']</t>
+        </is>
+      </c>
+      <c r="Q220" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="R220" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S220" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T220" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="U220" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V220" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="W220" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="X220" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y220" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z220" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA220" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AB220" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AC220" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AD220" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE220" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF220" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AG220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AH220" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI220" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ220" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AK220" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AL220" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM220" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AN220" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AP220" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="AQ220" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AR220" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AS220" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AT220" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AU220" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV220" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW220" t="n">
+        <v>6</v>
+      </c>
+      <c r="AX220" t="n">
+        <v>9</v>
+      </c>
+      <c r="AY220" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ220" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA220" t="n">
+        <v>4</v>
+      </c>
+      <c r="BB220" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC220" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BE220" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BF220" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BG220" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH220" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI220" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BJ220" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BK220" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="BL220" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="BM220" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN220" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO220" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP220" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>220</v>
+      </c>
+      <c r="B221" t="n">
+        <v>8227691</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E221" s="2" t="n">
+        <v>46088.47916666666</v>
+      </c>
+      <c r="F221" t="n">
+        <v>25</v>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I221" t="n">
+        <v>2</v>
+      </c>
+      <c r="J221" t="n">
+        <v>2</v>
+      </c>
+      <c r="K221" t="n">
+        <v>4</v>
+      </c>
+      <c r="L221" t="n">
+        <v>3</v>
+      </c>
+      <c r="M221" t="n">
+        <v>3</v>
+      </c>
+      <c r="N221" t="n">
+        <v>6</v>
+      </c>
+      <c r="O221" t="inlineStr">
+        <is>
+          <t>['34', '43', '86']</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>['37', '45+3', '52']</t>
+        </is>
+      </c>
+      <c r="Q221" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R221" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S221" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U221" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="V221" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="W221" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X221" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="Y221" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z221" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AA221" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AB221" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AC221" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AD221" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE221" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AF221" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AG221" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AH221" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AI221" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AJ221" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AK221" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL221" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN221" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AP221" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AQ221" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AR221" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AS221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AT221" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AU221" t="n">
+        <v>9</v>
+      </c>
+      <c r="AV221" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW221" t="n">
+        <v>13</v>
+      </c>
+      <c r="AX221" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY221" t="n">
+        <v>22</v>
+      </c>
+      <c r="AZ221" t="n">
+        <v>17</v>
+      </c>
+      <c r="BA221" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB221" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC221" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD221" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BE221" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BF221" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG221" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BH221" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BI221" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BJ221" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BK221" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BL221" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="BM221" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="BN221" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="BO221" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="BP221" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>221</v>
+      </c>
+      <c r="B222" t="n">
+        <v>8227584</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>46088.47916666666</v>
+      </c>
+      <c r="F222" t="n">
+        <v>25</v>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>Hamburger SV</t>
+        </is>
+      </c>
+      <c r="I222" t="n">
+        <v>1</v>
+      </c>
+      <c r="J222" t="n">
+        <v>1</v>
+      </c>
+      <c r="K222" t="n">
+        <v>2</v>
+      </c>
+      <c r="L222" t="n">
+        <v>1</v>
+      </c>
+      <c r="M222" t="n">
+        <v>2</v>
+      </c>
+      <c r="N222" t="n">
+        <v>3</v>
+      </c>
+      <c r="O222" t="inlineStr">
+        <is>
+          <t>['22']</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>['33', '58']</t>
+        </is>
+      </c>
+      <c r="Q222" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R222" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S222" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="T222" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="U222" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V222" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="W222" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="X222" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="Y222" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z222" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AA222" t="n">
+        <v>3.46</v>
+      </c>
+      <c r="AB222" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AC222" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AD222" t="n">
+        <v>12</v>
+      </c>
+      <c r="AE222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AF222" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AG222" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AH222" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AI222" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ222" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AK222" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AL222" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM222" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AN222" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP222" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AQ222" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="AR222" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AS222" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AT222" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="AU222" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV222" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW222" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX222" t="n">
+        <v>3</v>
+      </c>
+      <c r="AY222" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ222" t="n">
+        <v>10</v>
+      </c>
+      <c r="BA222" t="n">
+        <v>7</v>
+      </c>
+      <c r="BB222" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC222" t="n">
+        <v>10</v>
+      </c>
+      <c r="BD222" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="BE222" t="n">
+        <v>8</v>
+      </c>
+      <c r="BF222" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="BG222" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BH222" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="BI222" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BJ222" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BK222" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BL222" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="BM222" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BN222" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="BO222" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="BP222" t="n">
+        <v>1.42</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>222</v>
+      </c>
+      <c r="B223" t="n">
+        <v>8227811</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>46088.47916666666</v>
+      </c>
+      <c r="F223" t="n">
+        <v>25</v>
+      </c>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>Mainz 05</t>
+        </is>
+      </c>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I223" t="n">
+        <v>1</v>
+      </c>
+      <c r="J223" t="n">
+        <v>0</v>
+      </c>
+      <c r="K223" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" t="n">
+        <v>2</v>
+      </c>
+      <c r="M223" t="n">
+        <v>2</v>
+      </c>
+      <c r="N223" t="n">
+        <v>4</v>
+      </c>
+      <c r="O223" t="inlineStr">
+        <is>
+          <t>['39', '90+1']</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>['76', '77']</t>
+        </is>
+      </c>
+      <c r="Q223" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R223" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="S223" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T223" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U223" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="V223" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="W223" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X223" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y223" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z223" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA223" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB223" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC223" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AD223" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AE223" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AF223" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG223" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH223" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI223" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AJ223" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AK223" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AL223" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM223" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AN223" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AP223" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AQ223" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR223" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AS223" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AT223" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AU223" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV223" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW223" t="n">
+        <v>11</v>
+      </c>
+      <c r="AX223" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY223" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ223" t="n">
+        <v>11</v>
+      </c>
+      <c r="BA223" t="n">
+        <v>5</v>
+      </c>
+      <c r="BB223" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC223" t="n">
+        <v>11</v>
+      </c>
+      <c r="BD223" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="BE223" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BF223" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BG223" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BH223" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="BI223" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ223" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BK223" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="BL223" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="BM223" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="BN223" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO223" t="n">
+        <v>3</v>
+      </c>
+      <c r="BP223" t="n">
         <v>1.34</v>
       </c>
     </row>

--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP223"/>
+  <dimension ref="A1:BP224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2222,7 +2222,7 @@
         <v>1.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR8" t="n">
         <v>0</v>
@@ -4617,7 +4617,7 @@
         <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ19" t="n">
         <v>0.6899999999999999</v>
@@ -5492,7 +5492,7 @@
         <v>0.77</v>
       </c>
       <c r="AQ23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR23" t="n">
         <v>0.82</v>
@@ -9634,7 +9634,7 @@
         <v>1.08</v>
       </c>
       <c r="AQ42" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR42" t="n">
         <v>1.7</v>
@@ -10285,7 +10285,7 @@
         <v>0</v>
       </c>
       <c r="AP45" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ45" t="n">
         <v>1.38</v>
@@ -13119,7 +13119,7 @@
         <v>1</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ58" t="n">
         <v>0.83</v>
@@ -13994,7 +13994,7 @@
         <v>2.62</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR62" t="n">
         <v>2.7</v>
@@ -16610,7 +16610,7 @@
         <v>1.62</v>
       </c>
       <c r="AQ74" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR74" t="n">
         <v>1.45</v>
@@ -18133,7 +18133,7 @@
         <v>0.5</v>
       </c>
       <c r="AP81" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ81" t="n">
         <v>0.83</v>
@@ -19444,7 +19444,7 @@
         <v>1.46</v>
       </c>
       <c r="AQ87" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR87" t="n">
         <v>1.86</v>
@@ -21839,7 +21839,7 @@
         <v>1.6</v>
       </c>
       <c r="AP98" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ98" t="n">
         <v>1.17</v>
@@ -23586,7 +23586,7 @@
         <v>1.92</v>
       </c>
       <c r="AQ106" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR106" t="n">
         <v>1.85</v>
@@ -25545,7 +25545,7 @@
         <v>0.5</v>
       </c>
       <c r="AP115" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ115" t="n">
         <v>0.62</v>
@@ -27728,7 +27728,7 @@
         <v>2.08</v>
       </c>
       <c r="AQ125" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR125" t="n">
         <v>1.54</v>
@@ -28597,7 +28597,7 @@
         <v>1</v>
       </c>
       <c r="AP129" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ129" t="n">
         <v>0.92</v>
@@ -30344,7 +30344,7 @@
         <v>1.67</v>
       </c>
       <c r="AQ137" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR137" t="n">
         <v>1.54</v>
@@ -32957,7 +32957,7 @@
         <v>2.71</v>
       </c>
       <c r="AP149" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ149" t="n">
         <v>2.67</v>
@@ -34483,7 +34483,7 @@
         <v>0.75</v>
       </c>
       <c r="AP156" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ156" t="n">
         <v>0.83</v>
@@ -36884,7 +36884,7 @@
         <v>1.42</v>
       </c>
       <c r="AQ167" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR167" t="n">
         <v>1.38</v>
@@ -37971,7 +37971,7 @@
         <v>1.11</v>
       </c>
       <c r="AP172" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ172" t="n">
         <v>0.92</v>
@@ -40372,7 +40372,7 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="AQ183" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR183" t="n">
         <v>1.56</v>
@@ -41459,7 +41459,7 @@
         <v>1.5</v>
       </c>
       <c r="AP188" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ188" t="n">
         <v>1.75</v>
@@ -44075,7 +44075,7 @@
         <v>1.91</v>
       </c>
       <c r="AP200" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AQ200" t="n">
         <v>1.92</v>
@@ -44950,7 +44950,7 @@
         <v>2</v>
       </c>
       <c r="AQ204" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AR204" t="n">
         <v>1.99</v>
@@ -49110,13 +49110,13 @@
         <v>4</v>
       </c>
       <c r="AW223" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX223" t="n">
         <v>7</v>
       </c>
       <c r="AY223" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ223" t="n">
         <v>11</v>
@@ -49168,6 +49168,224 @@
       </c>
       <c r="BP223" t="n">
         <v>1.34</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>223</v>
+      </c>
+      <c r="B224" t="n">
+        <v>8227601</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Germany Bundesliga</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="n">
+        <v>46088.60416666666</v>
+      </c>
+      <c r="F224" t="n">
+        <v>25</v>
+      </c>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>Köln</t>
+        </is>
+      </c>
+      <c r="H224" t="inlineStr">
+        <is>
+          <t>Borussia Dortmund</t>
+        </is>
+      </c>
+      <c r="I224" t="n">
+        <v>0</v>
+      </c>
+      <c r="J224" t="n">
+        <v>1</v>
+      </c>
+      <c r="K224" t="n">
+        <v>1</v>
+      </c>
+      <c r="L224" t="n">
+        <v>1</v>
+      </c>
+      <c r="M224" t="n">
+        <v>2</v>
+      </c>
+      <c r="N224" t="n">
+        <v>3</v>
+      </c>
+      <c r="O224" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>['16', '60']</t>
+        </is>
+      </c>
+      <c r="Q224" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="R224" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S224" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="T224" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="U224" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V224" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="W224" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="X224" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="Y224" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Z224" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="AA224" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AB224" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC224" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AD224" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE224" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AF224" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AG224" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH224" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AI224" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AJ224" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AK224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AL224" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM224" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AN224" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AP224" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AQ224" t="n">
+        <v>2</v>
+      </c>
+      <c r="AR224" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AS224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AT224" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AU224" t="n">
+        <v>4</v>
+      </c>
+      <c r="AV224" t="n">
+        <v>5</v>
+      </c>
+      <c r="AW224" t="n">
+        <v>10</v>
+      </c>
+      <c r="AX224" t="n">
+        <v>8</v>
+      </c>
+      <c r="AY224" t="n">
+        <v>14</v>
+      </c>
+      <c r="AZ224" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA224" t="n">
+        <v>9</v>
+      </c>
+      <c r="BB224" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC224" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD224" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BE224" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="BF224" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG224" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BH224" t="n">
+        <v>3.53</v>
+      </c>
+      <c r="BI224" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BJ224" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BK224" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BL224" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="BM224" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="BN224" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="BO224" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="BP224" t="n">
+        <v>1.39</v>
       </c>
     </row>
   </sheetData>

--- a/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
+++ b/Bases_de_Dados/FootyStats/Germany Bundesliga_20252026.xlsx
@@ -48674,13 +48674,13 @@
         <v>5</v>
       </c>
       <c r="AW221" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX221" t="n">
         <v>12</v>
       </c>
       <c r="AY221" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ221" t="n">
         <v>17</v>
